--- a/Fase 1/Evidencias Grupales/Cronograma_Actividades_Equipo_PerfilMedico.xlsx
+++ b/Fase 1/Evidencias Grupales/Cronograma_Actividades_Equipo_PerfilMedico.xlsx
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD-MM-YYYY"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD-MM-YYYY"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -144,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -154,7 +153,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,7 +168,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,7 +183,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,6 +203,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -593,10 +601,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Metodología: Ágil (Scrum) · Sprints de 2 semanas · Asignatura PTY4614 · Equipo: Benjamín Leiva (Backend), Sergio Ocarez (BD + IA), Matías Pizarro (App móvil)</t>
-        </is>
-      </c>
-    </row>
+          <t>Metodología: Ágil (Scrum) · Sprints de 2 semanas · Asignatura PTY4614 · Equipo: Benjamín Leiva (Backend), Sergio Ocares (BD + IA), Matías Pizarro (App móvil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -643,10 +652,10 @@
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="22" t="n">
         <v>46244</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="22" t="n">
         <v>46249</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -679,10 +688,10 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="22" t="n">
         <v>46251</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="22" t="n">
         <v>46256</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -715,10 +724,10 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="22" t="n">
         <v>46258</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="22" t="n">
         <v>46263</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -751,10 +760,10 @@
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="22" t="n">
         <v>46265</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="22" t="n">
         <v>46270</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -787,10 +796,10 @@
       <c r="A9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="23" t="n">
         <v>46272</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="23" t="n">
         <v>46277</v>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -823,10 +832,10 @@
       <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="23" t="n">
         <v>46279</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="23" t="n">
         <v>46284</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -859,10 +868,10 @@
       <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="23" t="n">
         <v>46286</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="23" t="n">
         <v>46291</v>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -895,10 +904,10 @@
       <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="23" t="n">
         <v>46293</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="23" t="n">
         <v>46298</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -931,10 +940,10 @@
       <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="23" t="n">
         <v>46300</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="23" t="n">
         <v>46305</v>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -967,10 +976,10 @@
       <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="23" t="n">
         <v>46307</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="23" t="n">
         <v>46312</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1003,10 +1012,10 @@
       <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="23" t="n">
         <v>46314</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="23" t="n">
         <v>46319</v>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1039,10 +1048,10 @@
       <c r="A16" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="23" t="n">
         <v>46321</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="23" t="n">
         <v>46326</v>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1075,10 +1084,10 @@
       <c r="A17" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="23" t="n">
         <v>46328</v>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C17" s="23" t="n">
         <v>46333</v>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1111,10 +1120,10 @@
       <c r="A18" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="23" t="n">
         <v>46335</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="23" t="n">
         <v>46340</v>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1147,10 +1156,10 @@
       <c r="A19" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="23" t="n">
         <v>46342</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="23" t="n">
         <v>46347</v>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1183,10 +1192,10 @@
       <c r="A20" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="24" t="n">
         <v>46349</v>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="24" t="n">
         <v>46354</v>
       </c>
       <c r="D20" s="16" t="inlineStr">
@@ -1219,10 +1228,10 @@
       <c r="A21" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="15" t="n">
+      <c r="B21" s="24" t="n">
         <v>46356</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="24" t="n">
         <v>46361</v>
       </c>
       <c r="D21" s="16" t="inlineStr">
@@ -1255,10 +1264,10 @@
       <c r="A22" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="15" t="n">
+      <c r="B22" s="24" t="n">
         <v>46363</v>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C22" s="24" t="n">
         <v>46368</v>
       </c>
       <c r="D22" s="16" t="inlineStr">
@@ -1322,6 +1331,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1950,6 +1960,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1990,14 +2001,14 @@
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>Diseño de la API REST, autenticación JWT, control de acceso por roles, lógica de negocio (rutinas, alertas, permisos), integración con notificaciones push y con el módulo de IA.</t>
+          <t>Diseño de la API REST, autenticación JWT, control de acceso por roles, lógica de negocio (rutinas, alertas, permisos), orquestación técnica de la API de IA (envío de consultas y manejo de errores) e integración con notificaciones push.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>Sergio Ocarez</t>
+          <t>Sergio Ocares</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
@@ -2012,7 +2023,7 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>Modelado y administración de la base de datos, integridad y seguridad de la información, indicadores y reportes de cumplimiento, integración del módulo de inteligencia artificial.</t>
+          <t>Modelado y administración de la base de datos, integridad y seguridad de la información, indicadores y reportes de cumplimiento, definición del contexto de datos enviado a la IA y almacenamiento de sus resultados.</t>
         </is>
       </c>
     </row>
@@ -2038,6 +2049,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
         <is>

--- a/Fase 1/Evidencias Grupales/Cronograma_Actividades_Equipo_PerfilMedico.xlsx
+++ b/Fase 1/Evidencias Grupales/Cronograma_Actividades_Equipo_PerfilMedico.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Historial de cumplimiento y gráficos de indicadores (BD + Backend). Botón de asistencia (App)</t>
+          <t>Historial de cumplimiento y gráficos de indicadores (BD + Backend). Botón de asistencia (App). Modo "pantalla en casa" sobre tablet fija (App)</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Módulo de IA — orientación general (integración API LLM) y detección simple de patrones (BD + IA)</t>
+          <t>Módulo de IA — orientación general (integración API LLM) y detección simple de patrones (BD + IA). Integración con pulsera inteligente vía Health Connect (BD + Backend)</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Pruebas integrales, ajustes finales, documentación (manual técnico, Docker) y presentación del Informe Final</t>
+          <t>Detección de sonidos fuertes vía micrófono del dispositivo (App). Pruebas integrales, ajustes finales, documentación (manual técnico, Docker) y presentación del Informe Final</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -1312,7 +1312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1331,7 +1331,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1730,7 +1729,7 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>Como perfil dependiente (ej. adulto mayor) quiero una interfaz simplificada con botones grandes y confirmación en un toque</t>
+          <t>Como perfil dependiente (ej. adulto mayor) quiero una interfaz simplificada con botones grandes y confirmación en un toque, disponible también en modo "pantalla en casa" sobre una tablet fija (vía Fully Kiosk Browser) para quienes no manejan un smartphone</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -1926,6 +1925,76 @@
       <c r="G19" s="19" t="inlineStr">
         <is>
           <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pulsera inteligente</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Como titular o cuidador quiero ver signos vitales (frecuencia cardíaca) de un perfil desde una pulsera inteligente conectada, sin instrumentación adicional</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Perfil (titular/dependiente)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sergio (BD) / Benjamín (Backend)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Detección de ruido</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Como cuidador quiero recibir una alerta si el dispositivo del perfil dependiente detecta un sonido fuerte en el hogar (posible caída)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Perfil dependiente</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Matías (App) / Benjamín (Backend)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
     </row>
@@ -1960,7 +2029,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2049,7 +2117,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
         <is>
